--- a/DataTables/Datas/#Plane.xlsx
+++ b/DataTables/Datas/#Plane.xlsx
@@ -1319,10 +1319,10 @@
         <v>0.2</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>50000</v>
+        <v>50001</v>
       </c>
       <c r="J6">
         <v>20</v>
